--- a/hpi_scraper/JobsHiring/apollo/apollo_data.xlsx
+++ b/hpi_scraper/JobsHiring/apollo/apollo_data.xlsx
@@ -445,15 +445,15 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="51" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,49 +506,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>eng: 142; design: 13; it: 108; sales: 14; ops: 28</t>
+          <t>eng: 0; design: 0; it: 0; sales: 0; ops: 0</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>New Zealand; Sydney; Kuala Lumpur; Melbourne; Perth; Brisbane; Singapore; Port Macquarie; Toowoomba; Albury; Mandurah; Canberra; Bendigo; Bunbury; Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>https://groupcareers.singtel.com/job/Macquarie-Park-Business-Development-Manager-Macq/1363059166; https://groupcareers.singtel.com/job/Corporate-Counsel-Sydn/1363049066; https://groupcareers.singtel.com/job/Senior-Engineer%2C-IAM-Automation-%28Java-Python-Scripting%29-Kual/1363067966; https://groupcareers.singtel.com/job/Melbourne-Retail-Consultant%2C-Melbourne-Central-Melb/1362996966; https://groupcareers.singtel.com/job/Macquarie-Park-Manager-Carriage-Fulfilment-Macq/1363009966</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2"/>
